--- a/excel/group_without_date.xlsx
+++ b/excel/group_without_date.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6.26</v>
+        <v>30.48000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>32.365</v>
@@ -516,22 +516,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>ТД1--037409/1</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F4" t="n">
-        <v>32.365</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>45239</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -541,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -560,7 +554,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -579,22 +573,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>ТД1--040171/3</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="F7" t="n">
-        <v>32.365</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>45252</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -604,7 +592,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -623,22 +611,16 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>ТД1--041098/1</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>19.42</v>
-      </c>
-      <c r="F9" t="n">
-        <v>32.365</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>45258</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -648,7 +630,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -667,7 +649,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -686,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -705,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -724,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -743,16 +725,22 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>ТД1--025617/2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="F15" t="n">
+        <v>32.365</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>45233</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -762,22 +750,16 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>ТД1--045886/36</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="F16" t="n">
-        <v>32.365</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>45272</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -787,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -795,7 +777,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.12</v>
+        <v>96.62</v>
       </c>
       <c r="F17" t="n">
         <v>97.122</v>
@@ -812,7 +794,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -831,7 +813,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -850,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -869,7 +851,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -888,22 +870,16 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>ТД1--040103/2</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="F22" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>45248</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -913,22 +889,16 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>ТД1--032723/6</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="F23" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>45258</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -938,7 +908,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -957,7 +927,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -976,7 +946,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -995,7 +965,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1014,7 +984,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1033,22 +1003,16 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>ТД1--042023/2</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>40</v>
-      </c>
-      <c r="F29" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>45264</v>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1058,7 +1022,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1077,7 +1041,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1096,7 +1060,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1115,11 +1079,11 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ТД1--043456/1</t>
+          <t>ТД1--045886/17</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1134,22 +1098,16 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ТД1--045886/17</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>73.80000000000001</v>
-      </c>
-      <c r="F34" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>45272</v>
-      </c>
+          <t>ТД1--045886/21</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1159,16 +1117,22 @@
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ТД1--045886/21</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+          <t>ТД1--043456/1</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>97.122</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>45239</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -1178,7 +1142,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1197,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1216,7 +1180,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1235,7 +1199,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1243,7 +1207,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>22.7</v>
+        <v>43.50000000000001</v>
       </c>
       <c r="F39" t="n">
         <v>43.875</v>
@@ -1260,7 +1224,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1279,7 +1243,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1298,7 +1262,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1317,22 +1281,16 @@
         <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>ТД1--040103/5</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="F43" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>45248</v>
-      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -1342,11 +1300,11 @@
         <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ТД1--042618/1</t>
+          <t>ТД1--040171/2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1361,11 +1319,11 @@
         <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ТД1--040171/2</t>
+          <t>ТД1--039323/2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1380,22 +1338,16 @@
         <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ТД1--039323/2</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F46" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>45261</v>
-      </c>
+          <t>ТД1--042629/30</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -1405,11 +1357,11 @@
         <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ТД1--042629/30</t>
+          <t>ТД1--042629/31</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1424,11 +1376,11 @@
         <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ТД1--042629/31</t>
+          <t>ТД1--042629/32</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -1443,16 +1395,22 @@
         <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ТД1--042629/32</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+          <t>ТД1--042618/1</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="F49" t="n">
+        <v>43.875</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>45239</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -1462,7 +1420,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1481,22 +1439,16 @@
         <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>ТД1--042853/4</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="F51" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>45267</v>
-      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -1506,7 +1458,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1525,7 +1477,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1544,7 +1496,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1563,7 +1515,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1582,7 +1534,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1601,7 +1553,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1620,16 +1572,22 @@
         <v>2</v>
       </c>
       <c r="C58" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>ТД1--045886/31</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="F58" t="n">
+        <v>43.875</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>45239</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -1639,7 +1597,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1658,22 +1616,16 @@
         <v>2</v>
       </c>
       <c r="C60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>ТД1--045886/38</t>
         </is>
       </c>
-      <c r="E60" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F60" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>45267</v>
-      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -1683,7 +1635,7 @@
         <v>3</v>
       </c>
       <c r="C61" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1691,7 +1643,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>27.7</v>
+        <v>109.78</v>
       </c>
       <c r="F61" t="n">
         <v>110.997</v>
@@ -1708,7 +1660,7 @@
         <v>3</v>
       </c>
       <c r="C62" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1727,7 +1679,7 @@
         <v>3</v>
       </c>
       <c r="C63" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1746,22 +1698,16 @@
         <v>3</v>
       </c>
       <c r="C64" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>ТД1--040103/1</t>
         </is>
       </c>
-      <c r="E64" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="F64" t="n">
-        <v>110.997</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>45248</v>
-      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -1771,7 +1717,7 @@
         <v>3</v>
       </c>
       <c r="C65" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -1790,7 +1736,7 @@
         <v>3</v>
       </c>
       <c r="C66" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -1809,22 +1755,16 @@
         <v>3</v>
       </c>
       <c r="C67" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>ТД1--032723/1</t>
         </is>
       </c>
-      <c r="E67" t="n">
-        <v>106.91</v>
-      </c>
-      <c r="F67" t="n">
-        <v>110.997</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>45258</v>
-      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -1834,7 +1774,7 @@
         <v>3</v>
       </c>
       <c r="C68" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -1853,11 +1793,11 @@
         <v>3</v>
       </c>
       <c r="C69" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ТД1--032723/8</t>
+          <t>ТД1--045886/42</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -1872,16 +1812,22 @@
         <v>3</v>
       </c>
       <c r="C70" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ТД1--046586/1</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+          <t>ТД1--032723/8</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>107.33</v>
+      </c>
+      <c r="F70" t="n">
+        <v>110.997</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>45240</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -1891,11 +1837,11 @@
         <v>3</v>
       </c>
       <c r="C71" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ТД1--042629/19</t>
+          <t>ТД1--046586/1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -1910,11 +1856,11 @@
         <v>3</v>
       </c>
       <c r="C72" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ТД1--043925/5</t>
+          <t>ТД1--042629/19</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -1929,22 +1875,16 @@
         <v>3</v>
       </c>
       <c r="C73" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ТД1--042023/1</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F73" t="n">
-        <v>110.997</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>45264</v>
-      </c>
+          <t>ТД1--043925/5</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -1954,11 +1894,11 @@
         <v>3</v>
       </c>
       <c r="C74" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ТД1--044375/4</t>
+          <t>ТД1--042023/1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -1973,11 +1913,11 @@
         <v>3</v>
       </c>
       <c r="C75" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ТД1--044375/5</t>
+          <t>ТД1--044375/4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -1992,22 +1932,16 @@
         <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ТД1--045886/19</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>103.88</v>
-      </c>
-      <c r="F76" t="n">
-        <v>110.997</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>45272</v>
-      </c>
+          <t>ТД1--044375/5</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -2017,11 +1951,11 @@
         <v>3</v>
       </c>
       <c r="C77" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ТД1--045886/26</t>
+          <t>ТД1--045886/19</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -2036,11 +1970,11 @@
         <v>3</v>
       </c>
       <c r="C78" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ТД1--045886/27</t>
+          <t>ТД1--045886/26</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2055,7 +1989,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2074,16 +2008,22 @@
         <v>3</v>
       </c>
       <c r="C80" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ТД1--045886/42</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
+          <t>ТД1--045886/27</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>66.17999999999999</v>
+      </c>
+      <c r="F80" t="n">
+        <v>110.997</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>45240</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -2093,7 +2033,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2112,7 +2052,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2131,7 +2071,7 @@
         <v>4</v>
       </c>
       <c r="C83" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2156,7 +2096,7 @@
         <v>5</v>
       </c>
       <c r="C84" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2181,7 +2121,7 @@
         <v>6</v>
       </c>
       <c r="C85" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2206,7 +2146,7 @@
         <v>7</v>
       </c>
       <c r="C86" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2214,7 +2154,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F86" t="n">
         <v>38.39</v>
@@ -2231,22 +2171,16 @@
         <v>7</v>
       </c>
       <c r="C87" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
           <t>ТД1--043925/7</t>
         </is>
       </c>
-      <c r="E87" t="n">
-        <v>4</v>
-      </c>
-      <c r="F87" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>45261</v>
-      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -2256,7 +2190,7 @@
         <v>8</v>
       </c>
       <c r="C88" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2264,7 +2198,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1.7</v>
+        <v>41.10000000000001</v>
       </c>
       <c r="F88" t="n">
         <v>43.875</v>
@@ -2281,22 +2215,16 @@
         <v>8</v>
       </c>
       <c r="C89" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>ТД1--039203/9</t>
         </is>
       </c>
-      <c r="E89" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="F89" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>45239</v>
-      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -2306,7 +2234,7 @@
         <v>8</v>
       </c>
       <c r="C90" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2325,22 +2253,16 @@
         <v>8</v>
       </c>
       <c r="C91" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
           <t>ТД1--040171/1</t>
         </is>
       </c>
-      <c r="E91" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="F91" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>45252</v>
-      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -2350,22 +2272,16 @@
         <v>8</v>
       </c>
       <c r="C92" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>ТД1--042629/21</t>
         </is>
       </c>
-      <c r="E92" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F92" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>45261</v>
-      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -2375,7 +2291,7 @@
         <v>8</v>
       </c>
       <c r="C93" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2394,7 +2310,7 @@
         <v>8</v>
       </c>
       <c r="C94" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2413,7 +2329,7 @@
         <v>8</v>
       </c>
       <c r="C95" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2432,22 +2348,16 @@
         <v>8</v>
       </c>
       <c r="C96" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
           <t>ТД1--042853/7</t>
         </is>
       </c>
-      <c r="E96" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="F96" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>45267</v>
-      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -2457,7 +2367,7 @@
         <v>8</v>
       </c>
       <c r="C97" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -2476,7 +2386,7 @@
         <v>8</v>
       </c>
       <c r="C98" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2495,7 +2405,7 @@
         <v>8</v>
       </c>
       <c r="C99" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2514,7 +2424,7 @@
         <v>8</v>
       </c>
       <c r="C100" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2533,7 +2443,7 @@
         <v>8</v>
       </c>
       <c r="C101" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2552,7 +2462,7 @@
         <v>8</v>
       </c>
       <c r="C102" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -2571,16 +2481,22 @@
         <v>8</v>
       </c>
       <c r="C103" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
           <t>ТД1--045886/39</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+      <c r="E103" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F103" t="n">
+        <v>43.875</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>45226</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -2590,7 +2506,7 @@
         <v>9</v>
       </c>
       <c r="C104" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -2598,7 +2514,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>38.5</v>
+        <v>43.05</v>
       </c>
       <c r="F104" t="n">
         <v>43.875</v>
@@ -2615,7 +2531,7 @@
         <v>9</v>
       </c>
       <c r="C105" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -2634,7 +2550,7 @@
         <v>9</v>
       </c>
       <c r="C106" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -2653,7 +2569,7 @@
         <v>9</v>
       </c>
       <c r="C107" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -2672,7 +2588,7 @@
         <v>9</v>
       </c>
       <c r="C108" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -2691,7 +2607,7 @@
         <v>9</v>
       </c>
       <c r="C109" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -2710,22 +2626,16 @@
         <v>9</v>
       </c>
       <c r="C110" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ТД1--044744/6</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
-        <v>20</v>
-      </c>
-      <c r="F110" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G110" s="2" t="n">
-        <v>45241</v>
-      </c>
+          <t>ТД1--042629/25</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -2735,11 +2645,11 @@
         <v>9</v>
       </c>
       <c r="C111" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ТД1--044744/8</t>
+          <t>ТД1--043925/11</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -2754,21 +2664,21 @@
         <v>9</v>
       </c>
       <c r="C112" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ТД1--042629/20</t>
+          <t>ТД1--044744/6</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>29.85</v>
+        <v>37.09999999999999</v>
       </c>
       <c r="F112" t="n">
         <v>43.875</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>45251</v>
+        <v>45241</v>
       </c>
     </row>
     <row r="113">
@@ -2779,11 +2689,11 @@
         <v>9</v>
       </c>
       <c r="C113" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ТД1--042629/25</t>
+          <t>ТД1--044744/8</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -2798,11 +2708,11 @@
         <v>9</v>
       </c>
       <c r="C114" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ТД1--042629/26</t>
+          <t>ТД1--042629/20</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -2817,11 +2727,11 @@
         <v>9</v>
       </c>
       <c r="C115" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ТД1--042629/27</t>
+          <t>ТД1--042629/26</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -2836,11 +2746,11 @@
         <v>9</v>
       </c>
       <c r="C116" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ТД1--046886/2</t>
+          <t>ТД1--042629/27</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -2855,22 +2765,16 @@
         <v>9</v>
       </c>
       <c r="C117" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ТД1--041098/3</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="F117" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>45258</v>
-      </c>
+          <t>ТД1--045237/3</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -2880,16 +2784,22 @@
         <v>9</v>
       </c>
       <c r="C118" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ТД1--032723/5</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
+          <t>ТД1--046886/2</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="F118" t="n">
+        <v>43.875</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>45241</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -2899,11 +2809,11 @@
         <v>9</v>
       </c>
       <c r="C119" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ТД1--043925/11</t>
+          <t>ТД1--041098/3</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -2918,22 +2828,16 @@
         <v>9</v>
       </c>
       <c r="C120" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
           <t>ТД1--039323/3</t>
         </is>
       </c>
-      <c r="E120" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F120" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G120" s="2" t="n">
-        <v>45258</v>
-      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -2943,21 +2847,21 @@
         <v>9</v>
       </c>
       <c r="C121" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ТД1--045237/3</t>
+          <t>ТД1--032723/5</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2.55</v>
+        <v>23.5</v>
       </c>
       <c r="F121" t="n">
         <v>43.875</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>45270</v>
+        <v>45241</v>
       </c>
     </row>
     <row r="122">
@@ -2968,7 +2872,7 @@
         <v>10</v>
       </c>
       <c r="C122" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -2976,7 +2880,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4.2</v>
+        <v>36.86</v>
       </c>
       <c r="F122" t="n">
         <v>38.39</v>
@@ -2993,22 +2897,16 @@
         <v>10</v>
       </c>
       <c r="C123" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
           <t>ТД1--044810/2</t>
         </is>
       </c>
-      <c r="E123" t="n">
-        <v>35.16</v>
-      </c>
-      <c r="F123" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G123" s="2" t="n">
-        <v>45241</v>
-      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -3018,7 +2916,7 @@
         <v>10</v>
       </c>
       <c r="C124" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -3037,16 +2935,22 @@
         <v>10</v>
       </c>
       <c r="C125" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ТД1--044744/11</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+          <t>ТД1--044302/1</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="F125" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>45234</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -3056,22 +2960,16 @@
         <v>10</v>
       </c>
       <c r="C126" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ТД1--044302/1</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
-        <v>19.92</v>
-      </c>
-      <c r="F126" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G126" s="2" t="n">
-        <v>45241</v>
-      </c>
+          <t>ТД1--044744/11</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -3081,7 +2979,7 @@
         <v>10</v>
       </c>
       <c r="C127" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -3100,22 +2998,16 @@
         <v>10</v>
       </c>
       <c r="C128" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
           <t>ТД1--045957/1</t>
         </is>
       </c>
-      <c r="E128" t="n">
-        <v>15.96</v>
-      </c>
-      <c r="F128" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G128" s="2" t="n">
-        <v>45248</v>
-      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -3125,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="C129" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -3144,7 +3036,7 @@
         <v>10</v>
       </c>
       <c r="C130" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -3163,7 +3055,7 @@
         <v>10</v>
       </c>
       <c r="C131" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -3171,13 +3063,13 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>13.29</v>
+        <v>14.86</v>
       </c>
       <c r="F131" t="n">
         <v>38.39</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>45258</v>
+        <v>45234</v>
       </c>
     </row>
     <row r="132">
@@ -3188,7 +3080,7 @@
         <v>10</v>
       </c>
       <c r="C132" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -3207,7 +3099,7 @@
         <v>10</v>
       </c>
       <c r="C133" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -3226,7 +3118,7 @@
         <v>10</v>
       </c>
       <c r="C134" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -3245,7 +3137,7 @@
         <v>10</v>
       </c>
       <c r="C135" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -3264,22 +3156,16 @@
         <v>10</v>
       </c>
       <c r="C136" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
           <t>ТД1--045886/14</t>
         </is>
       </c>
-      <c r="E136" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="F136" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G136" s="2" t="n">
-        <v>45272</v>
-      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -3289,7 +3175,7 @@
         <v>11</v>
       </c>
       <c r="C137" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -3297,7 +3183,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>16.8</v>
+        <v>21.07</v>
       </c>
       <c r="F137" t="n">
         <v>32.365</v>
@@ -3314,7 +3200,7 @@
         <v>11</v>
       </c>
       <c r="C138" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -3333,22 +3219,16 @@
         <v>11</v>
       </c>
       <c r="C139" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
           <t>ТД1--043768/1</t>
         </is>
       </c>
-      <c r="E139" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="F139" t="n">
-        <v>32.365</v>
-      </c>
-      <c r="G139" s="2" t="n">
-        <v>45253</v>
-      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -3358,7 +3238,7 @@
         <v>12</v>
       </c>
       <c r="C140" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -3366,7 +3246,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4.3</v>
+        <v>24.2</v>
       </c>
       <c r="F140" t="n">
         <v>38.39</v>
@@ -3383,22 +3263,16 @@
         <v>12</v>
       </c>
       <c r="C141" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>ТД1--046603/1</t>
         </is>
       </c>
-      <c r="E141" t="n">
-        <v>20</v>
-      </c>
-      <c r="F141" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>45249</v>
-      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -3408,7 +3282,7 @@
         <v>12</v>
       </c>
       <c r="C142" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -3416,13 +3290,13 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>22.2</v>
+        <v>0.6</v>
       </c>
       <c r="F142" t="n">
         <v>38.39</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>45249</v>
+        <v>45241</v>
       </c>
     </row>
     <row r="143">
@@ -3433,7 +3307,7 @@
         <v>13</v>
       </c>
       <c r="C143" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -3441,7 +3315,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>15.3</v>
+        <v>95.99999999999999</v>
       </c>
       <c r="F143" t="n">
         <v>97.122</v>
@@ -3458,22 +3332,16 @@
         <v>13</v>
       </c>
       <c r="C144" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
           <t>ТД1--042629/22</t>
         </is>
       </c>
-      <c r="E144" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="F144" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>45261</v>
-      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -3483,7 +3351,7 @@
         <v>13</v>
       </c>
       <c r="C145" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -3502,7 +3370,7 @@
         <v>13</v>
       </c>
       <c r="C146" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -3521,7 +3389,7 @@
         <v>13</v>
       </c>
       <c r="C147" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -3540,7 +3408,7 @@
         <v>13</v>
       </c>
       <c r="C148" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -3559,22 +3427,16 @@
         <v>13</v>
       </c>
       <c r="C149" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ТД1--045601/2</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
-        <v>91.39999999999999</v>
-      </c>
-      <c r="F149" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>45271</v>
-      </c>
+          <t>ТД1--045601/3</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -3584,11 +3446,11 @@
         <v>13</v>
       </c>
       <c r="C150" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ТД1--045601/3</t>
+          <t>ТД1--045601/4</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -3603,11 +3465,11 @@
         <v>13</v>
       </c>
       <c r="C151" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ТД1--045601/4</t>
+          <t>ТД1--045886/25</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -3622,16 +3484,22 @@
         <v>13</v>
       </c>
       <c r="C152" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ТД1--045886/5</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
+          <t>ТД1--045601/2</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>95.10000000000001</v>
+      </c>
+      <c r="F152" t="n">
+        <v>97.122</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>45239</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -3641,11 +3509,11 @@
         <v>13</v>
       </c>
       <c r="C153" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ТД1--045886/18</t>
+          <t>ТД1--045886/5</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -3660,11 +3528,11 @@
         <v>13</v>
       </c>
       <c r="C154" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ТД1--045886/25</t>
+          <t>ТД1--045886/18</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -3679,22 +3547,16 @@
         <v>13</v>
       </c>
       <c r="C155" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
           <t>ТД1--045886/20</t>
         </is>
       </c>
-      <c r="E155" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="F155" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G155" s="2" t="n">
-        <v>45271</v>
-      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -3704,7 +3566,7 @@
         <v>13</v>
       </c>
       <c r="C156" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -3723,7 +3585,7 @@
         <v>13</v>
       </c>
       <c r="C157" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -3742,7 +3604,7 @@
         <v>14</v>
       </c>
       <c r="C158" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -3750,7 +3612,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>51</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F158" t="n">
         <v>97.122</v>
@@ -3767,7 +3629,7 @@
         <v>14</v>
       </c>
       <c r="C159" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -3786,22 +3648,16 @@
         <v>14</v>
       </c>
       <c r="C160" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
           <t>ТД1--043925/10</t>
         </is>
       </c>
-      <c r="E160" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F160" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G160" s="2" t="n">
-        <v>45261</v>
-      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -3811,22 +3667,16 @@
         <v>14</v>
       </c>
       <c r="C161" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
           <t>ТД1--045601/5</t>
         </is>
       </c>
-      <c r="E161" t="n">
-        <v>62.09999999999999</v>
-      </c>
-      <c r="F161" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G161" s="2" t="n">
-        <v>45271</v>
-      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -3836,7 +3686,7 @@
         <v>14</v>
       </c>
       <c r="C162" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -3855,11 +3705,11 @@
         <v>14</v>
       </c>
       <c r="C163" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ТД1--045886/22</t>
+          <t>ТД1--045886/30</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -3874,16 +3724,22 @@
         <v>14</v>
       </c>
       <c r="C164" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ТД1--045886/30</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
+          <t>ТД1--045886/22</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F164" t="n">
+        <v>97.122</v>
+      </c>
+      <c r="G164" s="2" t="n">
+        <v>45239</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -3893,7 +3749,7 @@
         <v>15</v>
       </c>
       <c r="C165" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -3901,7 +3757,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>35.5</v>
+        <v>37</v>
       </c>
       <c r="F165" t="n">
         <v>38.39</v>
@@ -3918,7 +3774,7 @@
         <v>15</v>
       </c>
       <c r="C166" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -3937,7 +3793,7 @@
         <v>15</v>
       </c>
       <c r="C167" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -3956,22 +3812,16 @@
         <v>15</v>
       </c>
       <c r="C168" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ТД1--044810/3</t>
-        </is>
-      </c>
-      <c r="E168" t="n">
-        <v>33.24</v>
-      </c>
-      <c r="F168" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G168" s="2" t="n">
-        <v>45241</v>
-      </c>
+          <t>ТД1--047617/2</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -3981,16 +3831,22 @@
         <v>15</v>
       </c>
       <c r="C169" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ТД1--045886/40</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
+          <t>ТД1--044744/5</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>36.58000000000001</v>
+      </c>
+      <c r="F169" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>45234</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -4000,11 +3856,11 @@
         <v>15</v>
       </c>
       <c r="C170" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ТД1--047617/2</t>
+          <t>ТД1--044744/9</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -4019,11 +3875,11 @@
         <v>15</v>
       </c>
       <c r="C171" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ТД1--044744/1</t>
+          <t>ТД1--044744/10</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -4038,11 +3894,11 @@
         <v>15</v>
       </c>
       <c r="C172" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>ТД1--044744/7</t>
+          <t>ТД1--043049/10</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -4057,11 +3913,11 @@
         <v>15</v>
       </c>
       <c r="C173" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ТД1--044744/10</t>
+          <t>ТД1--043049/11</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -4076,21 +3932,21 @@
         <v>15</v>
       </c>
       <c r="C174" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ТД1--044744/5</t>
+          <t>ТД1--045886/40</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>30</v>
+        <v>33.57</v>
       </c>
       <c r="F174" t="n">
         <v>38.39</v>
       </c>
       <c r="G174" s="2" t="n">
-        <v>45241</v>
+        <v>45234</v>
       </c>
     </row>
     <row r="175">
@@ -4101,11 +3957,11 @@
         <v>15</v>
       </c>
       <c r="C175" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ТД1--044744/9</t>
+          <t>ТД1--044744/1</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -4120,22 +3976,16 @@
         <v>15</v>
       </c>
       <c r="C176" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>ТД1--043049/10</t>
-        </is>
-      </c>
-      <c r="E176" t="n">
-        <v>35.55</v>
-      </c>
-      <c r="F176" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G176" s="2" t="n">
-        <v>45258</v>
-      </c>
+          <t>ТД1--043241/4</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -4145,16 +3995,22 @@
         <v>15</v>
       </c>
       <c r="C177" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ТД1--043049/11</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
+          <t>ТД1--044810/3</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>37.44</v>
+      </c>
+      <c r="F177" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="G177" s="2" t="n">
+        <v>45234</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -4164,7 +4020,7 @@
         <v>15</v>
       </c>
       <c r="C178" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -4183,16 +4039,22 @@
         <v>15</v>
       </c>
       <c r="C179" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ТД1--043049/13</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
+          <t>ТД1--044744/7</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="F179" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="G179" s="2" t="n">
+        <v>45234</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -4202,11 +4064,11 @@
         <v>15</v>
       </c>
       <c r="C180" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ТД1--032723/2</t>
+          <t>ТД1--032723/9</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -4221,16 +4083,22 @@
         <v>15</v>
       </c>
       <c r="C181" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ТД1--032723/9</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
+          <t>ТД1--043049/13</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="F181" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="G181" s="2" t="n">
+        <v>45234</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -4240,22 +4108,16 @@
         <v>15</v>
       </c>
       <c r="C182" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ТД1--032723/4</t>
-        </is>
-      </c>
-      <c r="E182" t="n">
-        <v>35.12</v>
-      </c>
-      <c r="F182" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G182" s="2" t="n">
-        <v>45258</v>
-      </c>
+          <t>ТД1--032723/2</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -4265,11 +4127,11 @@
         <v>15</v>
       </c>
       <c r="C183" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ТД1--043241/4</t>
+          <t>ТД1--032723/4</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -4284,7 +4146,7 @@
         <v>16</v>
       </c>
       <c r="C184" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -4309,7 +4171,7 @@
         <v>17</v>
       </c>
       <c r="C185" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -4334,7 +4196,7 @@
         <v>17</v>
       </c>
       <c r="C186" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -4353,7 +4215,7 @@
         <v>18</v>
       </c>
       <c r="C187" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -4378,7 +4240,7 @@
         <v>19</v>
       </c>
       <c r="C188" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -4403,7 +4265,7 @@
         <v>20</v>
       </c>
       <c r="C189" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -4428,7 +4290,7 @@
         <v>21</v>
       </c>
       <c r="C190" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -4453,7 +4315,7 @@
         <v>22</v>
       </c>
       <c r="C191" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -4478,7 +4340,7 @@
         <v>23</v>
       </c>
       <c r="C192" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -4503,7 +4365,7 @@
         <v>24</v>
       </c>
       <c r="C193" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -4528,7 +4390,7 @@
         <v>25</v>
       </c>
       <c r="C194" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -4553,7 +4415,7 @@
         <v>26</v>
       </c>
       <c r="C195" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -4578,7 +4440,7 @@
         <v>27</v>
       </c>
       <c r="C196" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -4603,7 +4465,7 @@
         <v>28</v>
       </c>
       <c r="C197" t="n">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -4628,7 +4490,7 @@
         <v>29</v>
       </c>
       <c r="C198" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>

--- a/excel/group_without_date.xlsx
+++ b/excel/group_without_date.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G198"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,17 +476,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ТД1--032820/3</t>
+          <t>ТД1--009043/1</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30.48000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="F2" t="n">
-        <v>32.365</v>
+        <v>110.997</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>45233</v>
+        <v>45402</v>
       </c>
     </row>
     <row r="3">
@@ -501,7 +501,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>001--001677/1</t>
+          <t>ТД1--011720/3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -513,33 +513,39 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ТД1--037409/1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>ТД1--010849/1</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ТД1--037409/2</t>
+          <t>ТД1--011549/1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -551,14 +557,14 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ТД1--037409/3</t>
+          <t>ТД1--012097/1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -570,14 +576,14 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ТД1--040171/3</t>
+          <t>ТД1--013389/1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -589,33 +595,39 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ТД1--042666/1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>ТД1--005811/1+</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="F8" t="n">
+        <v>52.255</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>45346</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ТД1--041098/1</t>
+          <t>ТД1--009012/4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -627,14 +639,14 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ТД1--032723/3</t>
+          <t>ТД1--010410/1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -646,14 +658,14 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ТД1--042629/34</t>
+          <t>ТД1--011067/1+</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -665,14 +677,14 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ТД1--042629/35</t>
+          <t>ТД1--010966/2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -684,14 +696,14 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ТД1--042629/36</t>
+          <t>ТД1--011860/1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -703,14 +715,14 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ТД1--042629/37</t>
+          <t>ТД1--012317/8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -722,24 +734,24 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ТД1--025617/2</t>
+          <t>ТД1--010360/1</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8.65</v>
+        <v>46.75</v>
       </c>
       <c r="F15" t="n">
-        <v>32.365</v>
+        <v>52.255</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>45233</v>
+        <v>45346</v>
       </c>
     </row>
     <row r="16">
@@ -747,14 +759,14 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ТД1--045886/36</t>
+          <t>ТД1--013270/1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -766,24 +778,24 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ТД1--037409/6</t>
+          <t>ТД1--012500/1</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>96.62</v>
+        <v>32.37</v>
       </c>
       <c r="F17" t="n">
-        <v>97.122</v>
+        <v>52.255</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>45239</v>
+        <v>45346</v>
       </c>
     </row>
     <row r="18">
@@ -791,33 +803,39 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ТД1--037409/7</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+          <t>ТД1--056558/27</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>37.94</v>
+      </c>
+      <c r="F18" t="n">
+        <v>43.875</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>45362</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ТД1--037409/8</t>
+          <t>ТД1--012362/1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -829,14 +847,14 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ТД1--039203/11</t>
+          <t>ТД1--011882/15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -848,14 +866,14 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ТД1--036370/2</t>
+          <t>ТД1--012763/1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -867,14 +885,14 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ТД1--040103/2</t>
+          <t>ТД1--010561/6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -886,14 +904,14 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ТД1--032723/6</t>
+          <t>ТД1--013217/18</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -905,33 +923,39 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ТД1--039323/1</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+          <t>ТД1--010251/1</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>22</v>
+      </c>
+      <c r="F24" t="n">
+        <v>43.875</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>45362</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ТД1--042629/28</t>
+          <t>ТД1--012317/4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -943,52 +967,64 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ТД1--042629/29</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+          <t>ТД1--010849/2</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>43.875</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ТД1--043925/3</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+          <t>ТД1--056651/1</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F27" t="n">
+        <v>110.997</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>45289</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ТД1--043925/4</t>
+          <t>ТД1--009853/10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1000,14 +1036,14 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ТД1--042023/2</t>
+          <t>ТД1--011882/9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1019,14 +1055,14 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ТД1--042853/1</t>
+          <t>ТД1--011882/11</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1038,14 +1074,14 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ТД1--042853/2</t>
+          <t>ТД1--011882/13</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1057,14 +1093,14 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ТД1--042853/3</t>
+          <t>ТД1--010242/21</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1076,14 +1112,14 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ТД1--045886/17</t>
+          <t>ТД1--010242/23</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1095,14 +1131,14 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ТД1--045886/21</t>
+          <t>ТД1--010251/2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1114,39 +1150,33 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ТД1--043456/1</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="F35" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>45239</v>
-      </c>
+          <t>ТД1--011524/1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ТД1--045886/29</t>
+          <t>ТД1--010637/1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1158,14 +1188,14 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ТД1--045886/33</t>
+          <t>ТД1--013217/11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1177,14 +1207,14 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ТД1--045886/37</t>
+          <t>ТД1--013217/12</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1196,24 +1226,24 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ТД1--037409/13</t>
+          <t>ТД1--052061/16</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>43.50000000000001</v>
+        <v>76</v>
       </c>
       <c r="F39" t="n">
-        <v>43.875</v>
+        <v>110.997</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>45239</v>
+        <v>45289</v>
       </c>
     </row>
     <row r="40">
@@ -1221,14 +1251,14 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ТД1--037409/14</t>
+          <t>ТД1--052061/29</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1240,14 +1270,14 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ТД1--039203/10</t>
+          <t>ТД1--052061/30</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1259,14 +1289,14 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ТД1--038329/1</t>
+          <t>ТД1--052061/31</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1278,14 +1308,14 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ТД1--040103/5</t>
+          <t>ТД1--006997/3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1297,14 +1327,14 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ТД1--040171/2</t>
+          <t>ТД1--006997/6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1316,14 +1346,14 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ТД1--039323/2</t>
+          <t>ТД1--006997/10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1335,14 +1365,14 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ТД1--042629/30</t>
+          <t>ТД1--006997/15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1354,14 +1384,14 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ТД1--042629/31</t>
+          <t>ТД1--008326/2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1373,58 +1403,58 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ТД1--042629/32</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+          <t>ТД1--052061/18</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="F48" t="n">
+        <v>97.122</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>45289</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ТД1--042618/1</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="F49" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>45239</v>
-      </c>
+          <t>ТД1--052061/22</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ТД1--042629/33</t>
+          <t>ТД1--008467/5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -1436,14 +1466,14 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ТД1--042853/4</t>
+          <t>ТД1--008467/1+</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -1455,14 +1485,14 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ТД1--042853/5</t>
+          <t>ТД1--006997/7</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1474,14 +1504,14 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ТД1--042853/6</t>
+          <t>ТД1--006997/11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -1493,14 +1523,14 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C54" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ТД1--045237/1</t>
+          <t>ТД1--009063/2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -1512,33 +1542,39 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ТД1--045237/2</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+          <t>ТД1--006997/12</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="F55" t="n">
+        <v>97.122</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>45289</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ТД1--045886/15</t>
+          <t>ТД1--006997/16</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -1550,14 +1586,14 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ТД1--045886/23</t>
+          <t>ТД1--008326/3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -1569,39 +1605,33 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C58" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ТД1--045886/31</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="F58" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>45239</v>
-      </c>
+          <t>ТД1--010248/1</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ТД1--045886/34</t>
+          <t>ТД1--010634/3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -1613,58 +1643,58 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ТД1--045886/38</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+          <t>ТД1--009853/13</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>32.365</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>45408</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ТД1--036370/1</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>109.78</v>
-      </c>
-      <c r="F61" t="n">
-        <v>110.997</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>45240</v>
-      </c>
+          <t>ТД1--009853/14</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ТД1--040516/3</t>
+          <t>ТД1--010561/3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -1676,14 +1706,14 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ТД1--044744/3</t>
+          <t>ТД1--010561/2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -1695,14 +1725,14 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ТД1--040103/1</t>
+          <t>ТД1--011103/3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -1714,14 +1744,14 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ТД1--040103/3</t>
+          <t>ТД1--012317/12</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -1733,14 +1763,14 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ТД1--040103/4</t>
+          <t>ТД1--012317/13</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -1752,33 +1782,39 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ТД1--032723/1</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+          <t>ТД1--005811/1</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>47.94</v>
+      </c>
+      <c r="F67" t="n">
+        <v>52.255</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>45346</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ТД1--032723/7</t>
+          <t>ТД1--009012/2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -1790,14 +1826,14 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ТД1--045886/42</t>
+          <t>ТД1--011067/1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -1809,39 +1845,33 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ТД1--032723/8</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>107.33</v>
-      </c>
-      <c r="F70" t="n">
-        <v>110.997</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>45240</v>
-      </c>
+          <t>ТД1--011860/2</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C71" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ТД1--046586/1</t>
+          <t>ТД1--013456/1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -1853,33 +1883,39 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C72" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ТД1--042629/19</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
+          <t>ТД1--010273/1</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F72" t="n">
+        <v>43.875</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>45415</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C73" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ТД1--043925/5</t>
+          <t>ТД1--010251/3</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -1891,14 +1927,14 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C74" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ТД1--042023/1</t>
+          <t>ТД1--010561/4</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -1910,14 +1946,14 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C75" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ТД1--044375/4</t>
+          <t>ТД1--012317/6</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -1929,14 +1965,14 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C76" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ТД1--044375/5</t>
+          <t>ТД1--012317/1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -1948,14 +1984,14 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C77" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ТД1--045886/19</t>
+          <t>ТД1--012317/2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -1967,14 +2003,14 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C78" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ТД1--045886/26</t>
+          <t>ТД1--012317/3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -1986,14 +2022,14 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C79" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ТД1--045886/41</t>
+          <t>ТД1--013217/19</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2005,162 +2041,150 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ТД1--045886/27</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>66.17999999999999</v>
-      </c>
-      <c r="F80" t="n">
-        <v>110.997</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>45240</v>
-      </c>
+          <t>ТД1--013217/20</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C81" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ТД1--044772/1</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
+          <t>ТД1--011997/1</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>7</v>
+      </c>
+      <c r="F81" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>45394</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C82" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ТД1--044772/2</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
+          <t>ТД1--012164/2</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>24</v>
+      </c>
+      <c r="F82" t="n">
+        <v>43.875</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>45404</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C83" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ТД1--038253/1</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="F83" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>45240</v>
-      </c>
+          <t>ТД1--012317/7</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C84" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ТД1--038253/2</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="F84" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>45240</v>
-      </c>
+          <t>ТД1--010242/16</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C85" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ТД1--039248/5</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F85" t="n">
-        <v>110.997</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>45247</v>
-      </c>
+          <t>ТД1--010242/17</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C86" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ТД1--040392/1</t>
+          <t>ТД1--008467/9</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>38.39</v>
+        <v>97.122</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>45250</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="87">
@@ -2168,58 +2192,58 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C87" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ТД1--043925/7</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
+          <t>ТД1--008467/10</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F87" t="n">
+        <v>129.496</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C88" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ТД1--040840/1</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>41.10000000000001</v>
-      </c>
-      <c r="F88" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>45226</v>
-      </c>
+          <t>ТД1--008467/12+</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C89" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ТД1--039203/9</t>
+          <t>ТД1--008467/11</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -2231,33 +2255,39 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C90" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ТД1--040516/5</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
+          <t>ТД1--008467/4+</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>134.1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>145.876</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C91" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ТД1--040171/1</t>
+          <t>ТД1--008467/1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -2269,14 +2299,14 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C92" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ТД1--042629/21</t>
+          <t>ТД1--008467/6+</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -2288,14 +2318,14 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C93" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ТД1--042629/38</t>
+          <t>ТД1--008467/7</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -2307,71 +2337,89 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ТД1--042629/39</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
+          <t>ТД1--009058/1</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="F94" t="n">
+        <v>145.876</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C95" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ТД1--042629/40</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
+          <t>ТД1--008467/5+</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F95" t="n">
+        <v>132.17</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C96" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ТД1--042853/7</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+          <t>ТД1--008467/12</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F96" t="n">
+        <v>148.671</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C97" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ТД1--042853/8</t>
+          <t>ТД1--008467/13</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -2383,90 +2431,114 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C98" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ТД1--042853/9</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+          <t>ТД1--008467/6</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="F98" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C99" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ТД1--043698/2</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
+          <t>ТД1--010686/1</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="F99" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C100" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ТД1--045886/16</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+          <t>ТД1--010686/1+</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="F100" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C101" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ТД1--045886/24</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
+          <t>ТД1--052116/1</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="F101" t="n">
+        <v>97.122</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>45275</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C102" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ТД1--045886/35</t>
+          <t>ТД1--009853/22</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -2478,83 +2550,77 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C103" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ТД1--045886/39</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F103" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>45226</v>
-      </c>
+          <t>ТД1--010242/11</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C104" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ТД1--044810/4</t>
-        </is>
-      </c>
-      <c r="E104" t="n">
-        <v>43.05</v>
-      </c>
-      <c r="F104" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G104" s="2" t="n">
-        <v>45241</v>
-      </c>
+          <t>ТД1--010242/18</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C105" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ТД1--040516/2</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+          <t>ТД1--009063/1</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="F105" t="n">
+        <v>97.122</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>45275</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C106" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ТД1--040516/4</t>
+          <t>ТД1--010242/6</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -2566,14 +2632,14 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C107" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ТД1--040516/6</t>
+          <t>ТД1--010242/10</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -2585,14 +2651,14 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C108" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ТД1--044744/2</t>
+          <t>ТД1--010242/4</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -2604,33 +2670,39 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C109" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ТД1--044744/4</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+          <t>ТД1--010248/2</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="F109" t="n">
+        <v>97.122</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>45275</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C110" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ТД1--042629/25</t>
+          <t>ТД1--012154/2</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -2642,58 +2714,58 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C111" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ТД1--043925/11</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+          <t>ТД1--010634/2</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>90.88</v>
+      </c>
+      <c r="F111" t="n">
+        <v>97.122</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>45275</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C112" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ТД1--044744/6</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
-        <v>37.09999999999999</v>
-      </c>
-      <c r="F112" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G112" s="2" t="n">
-        <v>45241</v>
-      </c>
+          <t>ТД1--010242/5</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C113" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ТД1--044744/8</t>
+          <t>ТД1--010840/4</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -2705,14 +2777,14 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C114" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ТД1--042629/20</t>
+          <t>ТД1--013217/14</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -2724,33 +2796,39 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C115" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ТД1--042629/26</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+          <t>ТД1--010840/2</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>55</v>
+      </c>
+      <c r="F115" t="n">
+        <v>97.122</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>45275</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C116" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ТД1--042629/27</t>
+          <t>ТД1--013217/16</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -2762,58 +2840,58 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C117" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ТД1--045237/3</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+          <t>ТД1--052061/14</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="F117" t="n">
+        <v>67.801</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>45289</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C118" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ТД1--046886/2</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
-        <v>39.55</v>
-      </c>
-      <c r="F118" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>45241</v>
-      </c>
+          <t>ТД1--052061/19</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C119" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ТД1--041098/3</t>
+          <t>ТД1--052061/23</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -2825,14 +2903,14 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C120" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ТД1--039323/3</t>
+          <t>ТД1--052061/27</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -2844,64 +2922,52 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C121" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ТД1--032723/5</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F121" t="n">
-        <v>43.875</v>
-      </c>
-      <c r="G121" s="2" t="n">
-        <v>45241</v>
-      </c>
+          <t>ТД1--006997/4</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C122" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ТД1--042666/3</t>
-        </is>
-      </c>
-      <c r="E122" t="n">
-        <v>36.86</v>
-      </c>
-      <c r="F122" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G122" s="2" t="n">
-        <v>45234</v>
-      </c>
+          <t>ТД1--006997/8</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C123" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ТД1--044810/2</t>
+          <t>ТД1--006997/13</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -2913,14 +2979,14 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C124" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ТД1--045383/1</t>
+          <t>ТД1--006997/14</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -2932,39 +2998,33 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C125" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ТД1--044302/1</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
-        <v>38.38</v>
-      </c>
-      <c r="F125" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G125" s="2" t="n">
-        <v>45234</v>
-      </c>
+          <t>ТД1--006997/17</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C126" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ТД1--044744/11</t>
+          <t>ТД1--006997/18</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -2976,14 +3036,14 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C127" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ТД1--045043/1</t>
+          <t>ТД1--006997/19</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -2995,33 +3055,39 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C128" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ТД1--045957/1</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
+          <t>ТД1--012164/1</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>8</v>
+      </c>
+      <c r="F128" t="n">
+        <v>51.187</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>45404</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C129" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ТД1--042044/2</t>
+          <t>ТД1--010541/1</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -3033,14 +3099,14 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C130" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ТД1--045022/1</t>
+          <t>ТД1--010242/19</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -3052,24 +3118,24 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C131" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ТД1--041098/6</t>
+          <t>ТД1--006432/7</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>14.86</v>
+        <v>1</v>
       </c>
       <c r="F131" t="n">
         <v>38.39</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>45234</v>
+        <v>45388</v>
       </c>
     </row>
     <row r="132">
@@ -3077,119 +3143,149 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C132" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ТД1--043049/6</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
+          <t>ТД1--009063/4</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>36</v>
+      </c>
+      <c r="F132" t="n">
+        <v>59.615</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>45396</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C133" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ТД1--043049/8</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
+          <t>ТД1--009058/5</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="F133" t="n">
+        <v>82.855</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>45397</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C134" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ТД1--043049/9</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
+          <t>ТД1--009058/3</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F134" t="n">
+        <v>68.702</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>45397</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C135" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ТД1--025617/1</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
+          <t>ТД1--009058/4</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="F135" t="n">
+        <v>82.855</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>45397</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C136" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ТД1--045886/14</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
+          <t>ТД1--009063/3</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F136" t="n">
+        <v>68.702</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>45396</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C137" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ТД1--035550/1</t>
+          <t>ТД1--010714/2</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>21.07</v>
+        <v>25.12</v>
       </c>
       <c r="F137" t="n">
-        <v>32.365</v>
+        <v>58.599</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>45247</v>
+        <v>45396</v>
       </c>
     </row>
     <row r="138">
@@ -3197,1314 +3293,24 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C138" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ТД1--041792/1</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="1" t="n">
-        <v>137</v>
-      </c>
-      <c r="B139" t="n">
-        <v>11</v>
-      </c>
-      <c r="C139" t="n">
-        <v>24</v>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>ТД1--043768/1</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="1" t="n">
-        <v>138</v>
-      </c>
-      <c r="B140" t="n">
-        <v>12</v>
-      </c>
-      <c r="C140" t="n">
-        <v>25</v>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>ТД1--044810/1</t>
-        </is>
-      </c>
-      <c r="E140" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="F140" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G140" s="2" t="n">
-        <v>45241</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="1" t="n">
-        <v>139</v>
-      </c>
-      <c r="B141" t="n">
-        <v>12</v>
-      </c>
-      <c r="C141" t="n">
-        <v>25</v>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>ТД1--046603/1</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="1" t="n">
-        <v>140</v>
-      </c>
-      <c r="B142" t="n">
-        <v>12</v>
-      </c>
-      <c r="C142" t="n">
-        <v>26</v>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>ТД1--042044/1</t>
-        </is>
-      </c>
-      <c r="E142" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F142" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G142" s="2" t="n">
-        <v>45241</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="1" t="n">
-        <v>141</v>
-      </c>
-      <c r="B143" t="n">
-        <v>13</v>
-      </c>
-      <c r="C143" t="n">
-        <v>27</v>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>ТД1--042348/4</t>
-        </is>
-      </c>
-      <c r="E143" t="n">
-        <v>95.99999999999999</v>
-      </c>
-      <c r="F143" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G143" s="2" t="n">
-        <v>45239</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="1" t="n">
-        <v>142</v>
-      </c>
-      <c r="B144" t="n">
-        <v>13</v>
-      </c>
-      <c r="C144" t="n">
-        <v>27</v>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>ТД1--042629/22</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="1" t="n">
-        <v>143</v>
-      </c>
-      <c r="B145" t="n">
-        <v>13</v>
-      </c>
-      <c r="C145" t="n">
-        <v>27</v>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>ТД1--042348/1</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="1" t="n">
-        <v>144</v>
-      </c>
-      <c r="B146" t="n">
-        <v>13</v>
-      </c>
-      <c r="C146" t="n">
-        <v>27</v>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>ТД1--042348/2</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="1" t="n">
-        <v>145</v>
-      </c>
-      <c r="B147" t="n">
-        <v>13</v>
-      </c>
-      <c r="C147" t="n">
-        <v>27</v>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>ТД1--044375/6</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="1" t="n">
-        <v>146</v>
-      </c>
-      <c r="B148" t="n">
-        <v>13</v>
-      </c>
-      <c r="C148" t="n">
-        <v>27</v>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>ТД1--044375/7</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="1" t="n">
-        <v>147</v>
-      </c>
-      <c r="B149" t="n">
-        <v>13</v>
-      </c>
-      <c r="C149" t="n">
-        <v>27</v>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>ТД1--045601/3</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="1" t="n">
-        <v>148</v>
-      </c>
-      <c r="B150" t="n">
-        <v>13</v>
-      </c>
-      <c r="C150" t="n">
-        <v>27</v>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>ТД1--045601/4</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="1" t="n">
-        <v>149</v>
-      </c>
-      <c r="B151" t="n">
-        <v>13</v>
-      </c>
-      <c r="C151" t="n">
-        <v>27</v>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>ТД1--045886/25</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="1" t="n">
-        <v>150</v>
-      </c>
-      <c r="B152" t="n">
-        <v>13</v>
-      </c>
-      <c r="C152" t="n">
-        <v>28</v>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>ТД1--045601/2</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
-        <v>95.10000000000001</v>
-      </c>
-      <c r="F152" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>45239</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="1" t="n">
-        <v>151</v>
-      </c>
-      <c r="B153" t="n">
-        <v>13</v>
-      </c>
-      <c r="C153" t="n">
-        <v>28</v>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>ТД1--045886/5</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="1" t="n">
-        <v>152</v>
-      </c>
-      <c r="B154" t="n">
-        <v>13</v>
-      </c>
-      <c r="C154" t="n">
-        <v>28</v>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>ТД1--045886/18</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="1" t="n">
-        <v>153</v>
-      </c>
-      <c r="B155" t="n">
-        <v>13</v>
-      </c>
-      <c r="C155" t="n">
-        <v>28</v>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>ТД1--045886/20</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="1" t="n">
-        <v>154</v>
-      </c>
-      <c r="B156" t="n">
-        <v>13</v>
-      </c>
-      <c r="C156" t="n">
-        <v>28</v>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>ТД1--045886/28</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="1" t="n">
-        <v>155</v>
-      </c>
-      <c r="B157" t="n">
-        <v>13</v>
-      </c>
-      <c r="C157" t="n">
-        <v>28</v>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>ТД1--045886/32</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="1" t="n">
-        <v>156</v>
-      </c>
-      <c r="B158" t="n">
-        <v>14</v>
-      </c>
-      <c r="C158" t="n">
-        <v>29</v>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>ТД1--042348/3</t>
-        </is>
-      </c>
-      <c r="E158" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="F158" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G158" s="2" t="n">
-        <v>45239</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="1" t="n">
-        <v>157</v>
-      </c>
-      <c r="B159" t="n">
-        <v>14</v>
-      </c>
-      <c r="C159" t="n">
-        <v>29</v>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>ТД1--042348/5</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="1" t="n">
-        <v>158</v>
-      </c>
-      <c r="B160" t="n">
-        <v>14</v>
-      </c>
-      <c r="C160" t="n">
-        <v>29</v>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>ТД1--043925/10</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="1" t="n">
-        <v>159</v>
-      </c>
-      <c r="B161" t="n">
-        <v>14</v>
-      </c>
-      <c r="C161" t="n">
-        <v>29</v>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>ТД1--045601/5</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="B162" t="n">
-        <v>14</v>
-      </c>
-      <c r="C162" t="n">
-        <v>29</v>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>ТД1--045886/4</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="1" t="n">
-        <v>161</v>
-      </c>
-      <c r="B163" t="n">
-        <v>14</v>
-      </c>
-      <c r="C163" t="n">
-        <v>29</v>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>ТД1--045886/30</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="1" t="n">
-        <v>162</v>
-      </c>
-      <c r="B164" t="n">
-        <v>14</v>
-      </c>
-      <c r="C164" t="n">
-        <v>30</v>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>ТД1--045886/22</t>
-        </is>
-      </c>
-      <c r="E164" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F164" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G164" s="2" t="n">
-        <v>45239</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="1" t="n">
-        <v>163</v>
-      </c>
-      <c r="B165" t="n">
-        <v>15</v>
-      </c>
-      <c r="C165" t="n">
-        <v>31</v>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>ТД1--042666/2</t>
-        </is>
-      </c>
-      <c r="E165" t="n">
-        <v>37</v>
-      </c>
-      <c r="F165" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G165" s="2" t="n">
-        <v>45234</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="1" t="n">
-        <v>164</v>
-      </c>
-      <c r="B166" t="n">
-        <v>15</v>
-      </c>
-      <c r="C166" t="n">
-        <v>31</v>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>ТД1--044611/1</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="1" t="n">
-        <v>165</v>
-      </c>
-      <c r="B167" t="n">
-        <v>15</v>
-      </c>
-      <c r="C167" t="n">
-        <v>31</v>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>ТД1--044611/2</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="1" t="n">
-        <v>166</v>
-      </c>
-      <c r="B168" t="n">
-        <v>15</v>
-      </c>
-      <c r="C168" t="n">
-        <v>31</v>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>ТД1--047617/2</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="1" t="n">
-        <v>167</v>
-      </c>
-      <c r="B169" t="n">
-        <v>15</v>
-      </c>
-      <c r="C169" t="n">
-        <v>32</v>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>ТД1--044744/5</t>
-        </is>
-      </c>
-      <c r="E169" t="n">
-        <v>36.58000000000001</v>
-      </c>
-      <c r="F169" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G169" s="2" t="n">
-        <v>45234</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="1" t="n">
-        <v>168</v>
-      </c>
-      <c r="B170" t="n">
-        <v>15</v>
-      </c>
-      <c r="C170" t="n">
-        <v>32</v>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>ТД1--044744/9</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="1" t="n">
-        <v>169</v>
-      </c>
-      <c r="B171" t="n">
-        <v>15</v>
-      </c>
-      <c r="C171" t="n">
-        <v>32</v>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>ТД1--044744/10</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="1" t="n">
-        <v>170</v>
-      </c>
-      <c r="B172" t="n">
-        <v>15</v>
-      </c>
-      <c r="C172" t="n">
-        <v>32</v>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>ТД1--043049/10</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="1" t="n">
-        <v>171</v>
-      </c>
-      <c r="B173" t="n">
-        <v>15</v>
-      </c>
-      <c r="C173" t="n">
-        <v>32</v>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>ТД1--043049/11</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="1" t="n">
-        <v>172</v>
-      </c>
-      <c r="B174" t="n">
-        <v>15</v>
-      </c>
-      <c r="C174" t="n">
-        <v>33</v>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>ТД1--045886/40</t>
-        </is>
-      </c>
-      <c r="E174" t="n">
-        <v>33.57</v>
-      </c>
-      <c r="F174" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G174" s="2" t="n">
-        <v>45234</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="1" t="n">
-        <v>173</v>
-      </c>
-      <c r="B175" t="n">
-        <v>15</v>
-      </c>
-      <c r="C175" t="n">
-        <v>33</v>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>ТД1--044744/1</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="1" t="n">
-        <v>174</v>
-      </c>
-      <c r="B176" t="n">
-        <v>15</v>
-      </c>
-      <c r="C176" t="n">
-        <v>33</v>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>ТД1--043241/4</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="1" t="n">
-        <v>175</v>
-      </c>
-      <c r="B177" t="n">
-        <v>15</v>
-      </c>
-      <c r="C177" t="n">
-        <v>34</v>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>ТД1--044810/3</t>
-        </is>
-      </c>
-      <c r="E177" t="n">
-        <v>37.44</v>
-      </c>
-      <c r="F177" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G177" s="2" t="n">
-        <v>45234</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="1" t="n">
-        <v>176</v>
-      </c>
-      <c r="B178" t="n">
-        <v>15</v>
-      </c>
-      <c r="C178" t="n">
-        <v>34</v>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>ТД1--043049/12</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="1" t="n">
-        <v>177</v>
-      </c>
-      <c r="B179" t="n">
-        <v>15</v>
-      </c>
-      <c r="C179" t="n">
-        <v>35</v>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>ТД1--044744/7</t>
-        </is>
-      </c>
-      <c r="E179" t="n">
-        <v>32.17</v>
-      </c>
-      <c r="F179" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G179" s="2" t="n">
-        <v>45234</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="1" t="n">
-        <v>178</v>
-      </c>
-      <c r="B180" t="n">
-        <v>15</v>
-      </c>
-      <c r="C180" t="n">
-        <v>35</v>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>ТД1--032723/9</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="1" t="n">
-        <v>179</v>
-      </c>
-      <c r="B181" t="n">
-        <v>15</v>
-      </c>
-      <c r="C181" t="n">
-        <v>36</v>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>ТД1--043049/13</t>
-        </is>
-      </c>
-      <c r="E181" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="F181" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G181" s="2" t="n">
-        <v>45234</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="B182" t="n">
-        <v>15</v>
-      </c>
-      <c r="C182" t="n">
-        <v>36</v>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>ТД1--032723/2</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="1" t="n">
-        <v>181</v>
-      </c>
-      <c r="B183" t="n">
-        <v>15</v>
-      </c>
-      <c r="C183" t="n">
-        <v>36</v>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>ТД1--032723/4</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="1" t="n">
-        <v>182</v>
-      </c>
-      <c r="B184" t="n">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>37</v>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>ТД1--043698/1</t>
-        </is>
-      </c>
-      <c r="E184" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F184" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G184" s="2" t="n">
-        <v>45268</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="1" t="n">
-        <v>183</v>
-      </c>
-      <c r="B185" t="n">
-        <v>17</v>
-      </c>
-      <c r="C185" t="n">
-        <v>38</v>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>ТД1--043925/8</t>
-        </is>
-      </c>
-      <c r="E185" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F185" t="n">
-        <v>51.187</v>
-      </c>
-      <c r="G185" s="2" t="n">
-        <v>45261</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="1" t="n">
-        <v>184</v>
-      </c>
-      <c r="B186" t="n">
-        <v>17</v>
-      </c>
-      <c r="C186" t="n">
-        <v>38</v>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>ТД1--043925/9</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="1" t="n">
-        <v>185</v>
-      </c>
-      <c r="B187" t="n">
-        <v>18</v>
-      </c>
-      <c r="C187" t="n">
-        <v>39</v>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>ТД1--043401/3</t>
-        </is>
-      </c>
-      <c r="E187" t="n">
-        <v>20.24</v>
-      </c>
-      <c r="F187" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G187" s="2" t="n">
-        <v>45232</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="1" t="n">
-        <v>186</v>
-      </c>
-      <c r="B188" t="n">
-        <v>19</v>
-      </c>
-      <c r="C188" t="n">
-        <v>40</v>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>ТД1--044816/2</t>
-        </is>
-      </c>
-      <c r="E188" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F188" t="n">
-        <v>84.074</v>
-      </c>
-      <c r="G188" s="2" t="n">
-        <v>45255</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="1" t="n">
-        <v>187</v>
-      </c>
-      <c r="B189" t="n">
-        <v>20</v>
-      </c>
-      <c r="C189" t="n">
-        <v>41</v>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>ТД1--045902/1</t>
-        </is>
-      </c>
-      <c r="E189" t="n">
-        <v>20.57</v>
-      </c>
-      <c r="F189" t="n">
-        <v>57.191</v>
-      </c>
-      <c r="G189" s="2" t="n">
-        <v>45255</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="1" t="n">
-        <v>188</v>
-      </c>
-      <c r="B190" t="n">
-        <v>21</v>
-      </c>
-      <c r="C190" t="n">
-        <v>42</v>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>ТД1--045902/2</t>
-        </is>
-      </c>
-      <c r="E190" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="F190" t="n">
-        <v>24.668</v>
-      </c>
-      <c r="G190" s="2" t="n">
-        <v>45255</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="1" t="n">
-        <v>189</v>
-      </c>
-      <c r="B191" t="n">
-        <v>22</v>
-      </c>
-      <c r="C191" t="n">
-        <v>43</v>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>ТД1--045902/3</t>
-        </is>
-      </c>
-      <c r="E191" t="n">
-        <v>44.94</v>
-      </c>
-      <c r="F191" t="n">
-        <v>57.191</v>
-      </c>
-      <c r="G191" s="2" t="n">
-        <v>45255</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="1" t="n">
-        <v>190</v>
-      </c>
-      <c r="B192" t="n">
-        <v>23</v>
-      </c>
-      <c r="C192" t="n">
-        <v>44</v>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>ТД1--035550/2</t>
-        </is>
-      </c>
-      <c r="E192" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="F192" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="G192" s="2" t="n">
-        <v>45247</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="1" t="n">
-        <v>191</v>
-      </c>
-      <c r="B193" t="n">
-        <v>24</v>
-      </c>
-      <c r="C193" t="n">
-        <v>45</v>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>ТД1--035550/3</t>
-        </is>
-      </c>
-      <c r="E193" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="F193" t="n">
-        <v>32.365</v>
-      </c>
-      <c r="G193" s="2" t="n">
-        <v>45247</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="1" t="n">
-        <v>192</v>
-      </c>
-      <c r="B194" t="n">
-        <v>25</v>
-      </c>
-      <c r="C194" t="n">
-        <v>46</v>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>ТД1--046355/1</t>
-        </is>
-      </c>
-      <c r="E194" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="F194" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G194" s="2" t="n">
-        <v>45257</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="1" t="n">
-        <v>193</v>
-      </c>
-      <c r="B195" t="n">
-        <v>26</v>
-      </c>
-      <c r="C195" t="n">
-        <v>47</v>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>ТД1--046355/2</t>
-        </is>
-      </c>
-      <c r="E195" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="F195" t="n">
-        <v>97.122</v>
-      </c>
-      <c r="G195" s="2" t="n">
-        <v>45257</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="1" t="n">
-        <v>194</v>
-      </c>
-      <c r="B196" t="n">
-        <v>27</v>
-      </c>
-      <c r="C196" t="n">
-        <v>48</v>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>ТД1--046355/3</t>
-        </is>
-      </c>
-      <c r="E196" t="n">
-        <v>50.38</v>
-      </c>
-      <c r="F196" t="n">
-        <v>69.622</v>
-      </c>
-      <c r="G196" s="2" t="n">
-        <v>45257</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="1" t="n">
-        <v>195</v>
-      </c>
-      <c r="B197" t="n">
-        <v>28</v>
-      </c>
-      <c r="C197" t="n">
-        <v>49</v>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>ТД1--046360/1</t>
-        </is>
-      </c>
-      <c r="E197" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="F197" t="n">
-        <v>57.191</v>
-      </c>
-      <c r="G197" s="2" t="n">
-        <v>45253</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="1" t="n">
-        <v>196</v>
-      </c>
-      <c r="B198" t="n">
-        <v>29</v>
-      </c>
-      <c r="C198" t="n">
-        <v>50</v>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>ТД1--047149/1</t>
-        </is>
-      </c>
-      <c r="E198" t="n">
-        <v>1</v>
-      </c>
-      <c r="F198" t="n">
-        <v>110.997</v>
-      </c>
-      <c r="G198" s="2" t="n">
-        <v>45275</v>
+          <t>ТД1--010248/3</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="F138" t="n">
+        <v>68.702</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>45404</v>
       </c>
     </row>
   </sheetData>

--- a/excel/group_without_date.xlsx
+++ b/excel/group_without_date.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G170"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,15 +450,20 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Группа</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Намотка</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Max намотка</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
@@ -469,24 +474,29 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ТД1--009043/1</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>19.5</v>
+          <t>ТД1--008467/10</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>(21, 6, 6, 630)</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>110.99692021316</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>45402</v>
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>129.4964069153533</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>45387</v>
       </c>
     </row>
     <row r="3">
@@ -494,43 +504,59 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ТД1--011720/3</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>ТД1--008467/5+</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>(21, 3.0, 6.0, 630)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ТД1--008467/4</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>97.08</v>
+          <t>ТД1--008467/12+</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>(21, 6.0, 6.0, 630)</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>97.12230518651501</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>45289</v>
+        <v>8.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>129.4964069153533</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>45387</v>
       </c>
     </row>
     <row r="5">
@@ -538,100 +564,143 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ТД1--006997/9</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>ТД1--008467/11</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(21, 6, 6, 630)</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ТД1--011882/14</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>ТД1--009043/1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>(21, 3, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>110.99692021316</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>45402</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ТД1--010561/5</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>ТД1--010251/2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>(21, 2, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>110.99692021316</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>45415</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ТД1--013217/15</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>ТД1--008326/2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>(21, 4, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" t="n">
+        <v>110.99692021316</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>45399</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ТД1--011720/3</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>(21, 3, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>3</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ТД1--010242/1</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>97</v>
-      </c>
-      <c r="F9" t="n">
-        <v>97.12230518651501</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>45289</v>
+      <c r="G9" t="n">
+        <v>110.99692021316</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>45407</v>
       </c>
     </row>
     <row r="10">
@@ -639,359 +708,485 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ТД1--010242/15</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>ТД1--006997/3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>(21, 4, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
+        <v>110.99692021316</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>45391</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ТД1--012154/3</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>ТД1--011524/1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>(21, 2, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>23</v>
+      </c>
+      <c r="G11" t="n">
+        <v>110.99692021316</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>45417</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ТД1--052061/15</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>97</v>
-      </c>
-      <c r="F12" t="n">
-        <v>97.12230518651501</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>45289</v>
-      </c>
+          <t>ТД1--013217/11</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>(21, 2, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ТД1--052061/20</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>ТД1--010242/21</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>(21, 2, 7, 630)</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ТД1--006997/5</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>ТД1--010242/23</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>(21, 2, 7, 630)</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ТД1--010242/22</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>ТД1--010637/1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>(21, 2, 7, 630)</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ТД1--012154/1</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+          <t>ТД1--008467/12</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>(21, 7, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ТД1--009853/8</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="F17" t="n">
-        <v>97.12230518651501</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>45289</v>
-      </c>
+          <t>ТД1--008467/13</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>(21, 7, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ТД1--011882/12</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+          <t>ТД1--013217/12</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>(21, 2, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>38</v>
+      </c>
+      <c r="G18" t="n">
+        <v>110.99692021316</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>45429</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ТД1--010242/24</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>ТД1--009853/10</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>(21, 2, 7, 630)</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ТД1--010242/7</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>ТД1--011882/9</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>(21, 2, 7, 630)</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ТД1--010242/8</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+          <t>ТД1--052061/16</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>(21, 4, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>33</v>
+      </c>
+      <c r="G21" t="n">
+        <v>110.99692021316</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>45289</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ТД1--010242/2</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>ТД1--006997/6</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>(21, 4, 7, 630)</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ТД1--012317/5</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+          <t>ТД1--011882/11</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>(21, 2, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>110.99692021316</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>45411</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ТД1--012317/11</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>ТД1--056651/1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>(21, 2, 7, 630)</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ТД1--013217/13</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+          <t>ТД1--006997/10</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>(21, 4, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>110.99692021316</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>45391</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ТД1--013217/17</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+          <t>ТД1--011882/13</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>(21, 2, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" t="n">
+        <v>110.99692021316</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>45411</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ТД1--009058/2</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>96.75999999999999</v>
+          <t>ТД1--006997/15</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>(21, 4, 7, 630)</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>97.12230518651501</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>45289</v>
+        <v>12</v>
+      </c>
+      <c r="G27" t="n">
+        <v>110.99692021316</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>45391</v>
       </c>
     </row>
     <row r="28">
@@ -999,57 +1194,72 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ТД1--010242/9</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>ТД1--052061/29</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>(21, 4, 7, 630)</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ТД1--010242/3</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>ТД1--052061/30</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>(21, 4, 7, 630)</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ТД1--010840/1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>ТД1--052061/31</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>(21, 4, 7, 630)</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -1059,35 +1269,57 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ТД1--010840/3</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+          <t>ТД1--011394/1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>45429</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ТД1--011394/1</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+          <t>ТД1--008326/3</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>(21, 5, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>15</v>
+      </c>
+      <c r="G32" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>45399</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1097,21 +1329,26 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ТД1--010634/1</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>96.60000000000001</v>
+          <t>ТД1--010561/5</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
       </c>
       <c r="F33" t="n">
+        <v>21</v>
+      </c>
+      <c r="G33" t="n">
         <v>97.12230518651501</v>
       </c>
-      <c r="G33" s="2" t="n">
-        <v>45289</v>
+      <c r="H33" s="2" t="n">
+        <v>45416</v>
       </c>
     </row>
     <row r="34">
@@ -1122,16 +1359,21 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ТД1--011882/10</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>ТД1--009853/8</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1141,122 +1383,158 @@
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ТД1--010637/2</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>ТД1--010242/22</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ТД1--010849/1</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="F36" t="n">
-        <v>38.3904926074233</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>45387</v>
-      </c>
+          <t>ТД1--010242/24</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ТД1--011549/1</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>ТД1--010637/2</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ТД1--012097/1</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+          <t>ТД1--008467/9</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>(21, 1, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ТД1--013389/1</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+          <t>ТД1--008467/4</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="G39" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ТД1--005811/1+</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>29.83</v>
+          <t>ТД1--008467/4</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
       </c>
       <c r="F40" t="n">
-        <v>38.3904926074233</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>45346</v>
+        <v>19.88</v>
+      </c>
+      <c r="G40" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>45387</v>
       </c>
     </row>
     <row r="41">
@@ -1264,119 +1542,179 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ТД1--009012/4</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+          <t>ТД1--008467/4+</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>(21, 6.0, 8.0, 630)</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ТД1--010410/1</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+          <t>ТД1--008467/5</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>(21, 5, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ТД1--011067/1+</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+          <t>ТД1--008467/1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>(21, 6, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>78</v>
+      </c>
+      <c r="G43" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C44" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ТД1--011860/1</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+          <t>ТД1--008467/1+</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>(21, 5.0, 8.0, 630)</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>10</v>
+      </c>
+      <c r="G44" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ТД1--012317/8</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+          <t>ТД1--008467/6</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>(21, 7, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="G45" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C46" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ТД1--010966/2</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>36.68</v>
+          <t>ТД1--008467/6</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>(21, 7, 8, 630)</t>
+        </is>
       </c>
       <c r="F46" t="n">
-        <v>38.3904926074233</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>45346</v>
+        <v>91.88</v>
+      </c>
+      <c r="G46" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>45387</v>
       </c>
     </row>
     <row r="47">
@@ -1384,68 +1722,83 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ТД1--013270/1</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+          <t>ТД1--008467/6+</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>(21, 6.0, 8.0, 630)</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="G47" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ТД1--010360/1</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="F48" t="n">
-        <v>38.3904926074233</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>45346</v>
-      </c>
+          <t>ТД1--008467/7</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>(21, 6, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ТД1--012500/1</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>32.37</v>
+          <t>ТД1--013217/13</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
       </c>
       <c r="F49" t="n">
-        <v>38.3904926074233</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>45346</v>
+        <v>82</v>
+      </c>
+      <c r="G49" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>45429</v>
       </c>
     </row>
     <row r="50">
@@ -1453,447 +1806,569 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ТД1--056558/27</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>37.94</v>
-      </c>
-      <c r="F50" t="n">
-        <v>43.87484869419806</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>45362</v>
-      </c>
+          <t>ТД1--010242/7</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ТД1--012362/1</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>ТД1--010242/8</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ТД1--011882/15</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>ТД1--010242/9</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ТД1--012763/1</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>ТД1--012154/1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C54" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ТД1--010561/6</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+          <t>ТД1--010840/4</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>86</v>
+      </c>
+      <c r="G54" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>45416</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C55" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ТД1--013217/18</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>ТД1--013217/14</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C56" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ТД1--010251/1</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>22</v>
-      </c>
-      <c r="F56" t="n">
-        <v>43.87484869419806</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>45362</v>
-      </c>
+          <t>ТД1--009853/22</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C57" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ТД1--012317/4</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>ТД1--010242/6</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C58" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ТД1--010849/2</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F58" t="n">
-        <v>43.87484869419806</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>45387</v>
-      </c>
+          <t>ТД1--010242/10</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C59" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ТД1--056651/1</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="F59" t="n">
-        <v>110.99692021316</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>45289</v>
-      </c>
+          <t>ТД1--010242/11</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C60" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ТД1--009853/10</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>ТД1--012154/2</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ТД1--011882/9</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+          <t>ТД1--011882/10</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="G61" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>45411</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ТД1--011882/11</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t>ТД1--052061/15</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ТД1--011882/13</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>ТД1--006997/5</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ТД1--010242/21</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
+          <t>ТД1--013217/15</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ТД1--010242/23</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
+          <t>ТД1--010242/2</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ТД1--010251/2</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
+          <t>ТД1--010242/3</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ТД1--011524/1</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+          <t>ТД1--012154/3</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>15</v>
+      </c>
+      <c r="G67" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>45411</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C68" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ТД1--010637/1</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+          <t>ТД1--052061/18</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>(21, 5, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>18</v>
+      </c>
+      <c r="G68" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>45289</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C69" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ТД1--013217/11</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+          <t>ТД1--013217/16</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>15</v>
+      </c>
+      <c r="G69" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>45429</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C70" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ТД1--013217/12</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+          <t>ТД1--006997/7</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>(21, 5, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>15</v>
+      </c>
+      <c r="G70" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>45391</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C71" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ТД1--052061/16</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>76</v>
+          <t>ТД1--010242/4</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
       </c>
       <c r="F71" t="n">
-        <v>110.99692021316</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>45289</v>
+        <v>18</v>
+      </c>
+      <c r="G71" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>45414</v>
       </c>
     </row>
     <row r="72">
@@ -1901,176 +2376,239 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C72" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ТД1--052061/29</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+          <t>ТД1--010242/5</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ТД1--052061/30</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
+          <t>ТД1--011882/12</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="G73" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>45411</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ТД1--052061/31</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>ТД1--052061/20</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ТД1--006997/3</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+          <t>ТД1--006997/9</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ТД1--006997/6</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
+          <t>ТД1--010242/1</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>80</v>
+      </c>
+      <c r="G76" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>45411</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C77" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ТД1--006997/10</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
+          <t>ТД1--052061/22</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>(21, 5, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>18</v>
+      </c>
+      <c r="G77" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>45289</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C78" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ТД1--006997/15</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>ТД1--006997/11</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>(21, 5, 8, 630)</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C79" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ТД1--008326/2</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>ТД1--006997/12</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>(21, 5, 8, 630)</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ТД1--052061/18</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>95.90000000000001</v>
+          <t>ТД1--011882/14</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
       </c>
       <c r="F80" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G80" t="n">
         <v>97.12230518651501</v>
       </c>
-      <c r="G80" s="2" t="n">
-        <v>45289</v>
+      <c r="H80" s="2" t="n">
+        <v>45411</v>
       </c>
     </row>
     <row r="81">
@@ -2078,19 +2616,24 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ТД1--052061/22</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t>ТД1--012317/5</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -2100,116 +2643,164 @@
         <v>8</v>
       </c>
       <c r="C82" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ТД1--008467/5</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
+          <t>ТД1--006997/16</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>(21, 5, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>6</v>
+      </c>
+      <c r="G82" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>45391</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ТД1--008467/1+</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
+          <t>ТД1--012317/11</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>60</v>
+      </c>
+      <c r="G83" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>45427</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ТД1--006997/7</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+          <t>ТД1--010840/1</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ТД1--006997/11</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>ТД1--013217/17</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C86" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ТД1--009063/2</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
+          <t>ТД1--010840/2</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>40</v>
+      </c>
+      <c r="G86" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>45416</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ТД1--006997/12</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>96.88</v>
+          <t>ТД1--010840/3</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
       </c>
       <c r="F87" t="n">
+        <v>17</v>
+      </c>
+      <c r="G87" t="n">
         <v>97.12230518651501</v>
       </c>
-      <c r="G87" s="2" t="n">
-        <v>45289</v>
+      <c r="H87" s="2" t="n">
+        <v>45416</v>
       </c>
     </row>
     <row r="88">
@@ -2217,100 +2808,143 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ТД1--006997/16</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+          <t>ТД1--010242/15</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C89" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ТД1--008326/3</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
+          <t>ТД1--010242/18</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G89" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>45414</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ТД1--010248/1</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
+          <t>ТД1--010634/1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G90" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>45406</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ТД1--010634/3</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+          <t>ТД1--009058/2</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="G91" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>45397</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ТД1--009853/13</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>15.1</v>
+          <t>ТД1--009058/2</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
       </c>
       <c r="F92" t="n">
-        <v>32.36540620564671</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>45408</v>
+        <v>97.12230518651501</v>
+      </c>
+      <c r="G92" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>45397</v>
       </c>
     </row>
     <row r="93">
@@ -2318,138 +2952,209 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ТД1--009853/14</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+          <t>ТД1--009058/2</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>(21, 2, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="G93" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>45406</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C94" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ТД1--010561/3</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
+          <t>ТД1--052116/1</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G94" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>45275</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C95" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ТД1--010561/2</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
+          <t>ТД1--010634/2</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="G95" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>45406</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C96" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ТД1--011103/3</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+          <t>ТД1--010634/2</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="G96" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>45275</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C97" t="n">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ТД1--012317/12</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+          <t>ТД1--009063/1</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="G97" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>45275</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C98" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ТД1--012317/13</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+          <t>ТД1--010248/2</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>(21, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G98" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>45275</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C99" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ТД1--005811/1</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
-        <v>37.14</v>
+          <t>ТД1--010634/3</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>(21, 5, 8, 630)</t>
+        </is>
       </c>
       <c r="F99" t="n">
-        <v>38.3904926074233</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>45346</v>
+        <v>97.12230518651501</v>
+      </c>
+      <c r="G99" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>45406</v>
       </c>
     </row>
     <row r="100">
@@ -2457,81 +3162,119 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C100" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ТД1--009012/2</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+          <t>ТД1--010634/3</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>(21, 5, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="G100" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>45406</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C101" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ТД1--011067/1</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
+          <t>ТД1--009063/2</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>(21, 5, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="G101" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>45406</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C102" t="n">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ТД1--011860/2</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+          <t>ТД1--010248/1</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>(21, 5, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="G102" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>45406</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ТД1--013456/1</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
-        <v>10.8</v>
+          <t>ТД1--009058/1</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>(21, 6, 8, 630)</t>
+        </is>
       </c>
       <c r="F103" t="n">
-        <v>38.3904926074233</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>45346</v>
+        <v>97.12230518651501</v>
+      </c>
+      <c r="G103" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>45397</v>
       </c>
     </row>
     <row r="104">
@@ -2539,24 +3282,29 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ТД1--010273/1</t>
-        </is>
-      </c>
-      <c r="E104" t="n">
-        <v>23.5</v>
+          <t>ТД1--009058/1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>(21, 6, 8, 630)</t>
+        </is>
       </c>
       <c r="F104" t="n">
-        <v>43.87484869419806</v>
-      </c>
-      <c r="G104" s="2" t="n">
-        <v>45415</v>
+        <v>30.23</v>
+      </c>
+      <c r="G104" t="n">
+        <v>97.12230518651501</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>45397</v>
       </c>
     </row>
     <row r="105">
@@ -2564,176 +3312,269 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C105" t="n">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ТД1--010251/3</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+          <t>ТД1--009063/4</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>(20, 2, 8, 500)</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>36</v>
+      </c>
+      <c r="G105" t="n">
+        <v>83.46132774006608</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>45396</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C106" t="n">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ТД1--010561/4</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+          <t>ТД1--009058/5</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>(20, 2, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>82.85543988645556</v>
+      </c>
+      <c r="G106" t="n">
+        <v>82.85543988645556</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>45397</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C107" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ТД1--012317/6</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+          <t>ТД1--009058/5</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>(20, 2, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="G107" t="n">
+        <v>82.85543988645556</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>45397</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C108" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ТД1--012317/1</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
+          <t>ТД1--009058/4</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>(20, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="G108" t="n">
+        <v>82.85543988645556</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>45397</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C109" t="n">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ТД1--012317/2</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+          <t>ТД1--010248/3</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>(19, 1, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>68.70249815154163</v>
+      </c>
+      <c r="G109" t="n">
+        <v>68.70249815154163</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>45404</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C110" t="n">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ТД1--012317/3</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+          <t>ТД1--010248/3</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>(19, 1, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>68.70249815154163</v>
+      </c>
+      <c r="G110" t="n">
+        <v>68.70249815154163</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>45404</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C111" t="n">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ТД1--013217/19</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+          <t>ТД1--010248/3</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>(19, 1, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="G111" t="n">
+        <v>68.70249815154163</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>45404</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C112" t="n">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ТД1--013217/20</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+          <t>ТД1--009063/3</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>(19, 6, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G112" t="n">
+        <v>68.70249815154163</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>45396</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C113" t="n">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ТД1--010686/1+</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
-        <v>12.85</v>
+          <t>ТД1--009058/3</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>(19, 2, 8, 630)</t>
+        </is>
       </c>
       <c r="F113" t="n">
-        <v>38.3904926074233</v>
-      </c>
-      <c r="G113" s="2" t="n">
-        <v>45387</v>
+        <v>68.70249815154163</v>
+      </c>
+      <c r="G113" t="n">
+        <v>68.70249815154163</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>45397</v>
       </c>
     </row>
     <row r="114">
@@ -2741,43 +3582,59 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C114" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ТД1--011997/1</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+          <t>ТД1--009058/3</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>(19, 2, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>68.70249815154163</v>
+      </c>
+      <c r="G114" t="n">
+        <v>68.70249815154163</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>45397</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C115" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ТД1--012164/2</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
-        <v>24</v>
+          <t>ТД1--009058/3</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>(19, 2, 8, 630)</t>
+        </is>
       </c>
       <c r="F115" t="n">
-        <v>43.87484869419806</v>
-      </c>
-      <c r="G115" s="2" t="n">
-        <v>45404</v>
+        <v>10.1</v>
+      </c>
+      <c r="G115" t="n">
+        <v>68.70249815154163</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>45397</v>
       </c>
     </row>
     <row r="116">
@@ -2785,251 +3642,299 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C116" t="n">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ТД1--012317/7</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+          <t>ТД1--006997/19</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>(19, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="G116" t="n">
+        <v>67.80149153191225</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>45391</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C117" t="n">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ТД1--010242/16</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>ТД1--006997/18</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>(19, 3, 8, 630)</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C118" t="n">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ТД1--010242/17</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>ТД1--006997/17</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>(19, 3, 8, 630)</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C119" t="n">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ТД1--008467/9</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
-        <v>1</v>
-      </c>
-      <c r="F119" t="n">
-        <v>97.12230518651501</v>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>45387</v>
-      </c>
+          <t>ТД1--052061/27</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>(19, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C120" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ТД1--008467/10</t>
-        </is>
-      </c>
-      <c r="E120" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F120" t="n">
-        <v>129.4964069153533</v>
-      </c>
-      <c r="G120" s="2" t="n">
-        <v>45387</v>
-      </c>
+          <t>ТД1--006997/14</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>(19, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C121" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ТД1--008467/12+</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>ТД1--006997/13</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>(19, 3, 8, 630)</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C122" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ТД1--008467/11</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>ТД1--052061/23</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>(19, 3, 8, 630)</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C123" t="n">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ТД1--008467/4+</t>
-        </is>
-      </c>
-      <c r="E123" t="n">
-        <v>86.33</v>
-      </c>
-      <c r="F123" t="n">
-        <v>97.12230518651501</v>
-      </c>
-      <c r="G123" s="2" t="n">
-        <v>45387</v>
-      </c>
+          <t>ТД1--006997/8</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>(19, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C124" t="n">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ТД1--008467/6+</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
+          <t>ТД1--052061/19</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>(19, 3, 8, 630)</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C125" t="n">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ТД1--008467/7</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
+          <t>ТД1--006997/4</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>(19, 3, 8, 630)</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C126" t="n">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ТД1--009058/1</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
+          <t>ТД1--052061/14</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>(19, 3, 8, 630)</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C127" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ТД1--008467/1</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
-        <v>78</v>
+          <t>ТД1--010714/2</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>(18, 8, 8, 630)</t>
+        </is>
       </c>
       <c r="F127" t="n">
-        <v>97.12230518651501</v>
-      </c>
-      <c r="G127" s="2" t="n">
-        <v>45387</v>
+        <v>58.5990951137035</v>
+      </c>
+      <c r="G127" t="n">
+        <v>58.5990951137035</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>45396</v>
       </c>
     </row>
     <row r="128">
@@ -3037,24 +3942,29 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C128" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ТД1--008467/5+</t>
-        </is>
-      </c>
-      <c r="E128" t="n">
-        <v>2.5</v>
+          <t>ТД1--010714/2</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>(18, 8, 8, 630)</t>
+        </is>
       </c>
       <c r="F128" t="n">
-        <v>97.12230518651501</v>
-      </c>
-      <c r="G128" s="2" t="n">
-        <v>45387</v>
+        <v>25.12</v>
+      </c>
+      <c r="G128" t="n">
+        <v>58.5990951137035</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>45396</v>
       </c>
     </row>
     <row r="129">
@@ -3062,24 +3972,29 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C129" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ТД1--008467/12</t>
-        </is>
-      </c>
-      <c r="E129" t="n">
-        <v>3.8</v>
+          <t>ТД1--009853/14</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>(15, 7, 8, 630)</t>
+        </is>
       </c>
       <c r="F129" t="n">
-        <v>97.12230518651501</v>
-      </c>
-      <c r="G129" s="2" t="n">
-        <v>45387</v>
+        <v>15.1</v>
+      </c>
+      <c r="G129" t="n">
+        <v>32.36540620564671</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>45408</v>
       </c>
     </row>
     <row r="130">
@@ -3087,175 +4002,203 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C130" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ТД1--008467/13</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>ТД1--009853/13</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>(15, 7, 8, 630)</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C131" t="n">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ТД1--008467/6</t>
-        </is>
-      </c>
-      <c r="E131" t="n">
-        <v>91.88</v>
-      </c>
-      <c r="F131" t="n">
-        <v>97.12230518651501</v>
-      </c>
-      <c r="G131" s="2" t="n">
-        <v>45387</v>
-      </c>
+          <t>ТД1--012317/13</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>(15, 7, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C132" t="n">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ТД1--010686/1</t>
-        </is>
-      </c>
-      <c r="E132" t="n">
-        <v>12.15</v>
-      </c>
-      <c r="F132" t="n">
-        <v>38.3904926074233</v>
-      </c>
-      <c r="G132" s="2" t="n">
-        <v>45387</v>
-      </c>
+          <t>ТД1--012317/12</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>(15, 7, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C133" t="n">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ТД1--052116/1</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="F133" t="n">
-        <v>97.12230518651501</v>
-      </c>
-      <c r="G133" s="2" t="n">
-        <v>45275</v>
-      </c>
+          <t>ТД1--011103/3</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>(15, 7, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C134" t="n">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ТД1--009853/22</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>ТД1--010561/2</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>(15, 7, 8, 630)</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C135" t="n">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ТД1--010242/11</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+          <t>ТД1--010561/3</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>(15, 7, 8, 630)</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C136" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ТД1--010242/18</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
+          <t>ТД1--006432/7</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>(16, 1, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>45388</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C137" t="n">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ТД1--009063/1</t>
-        </is>
-      </c>
-      <c r="E137" t="n">
-        <v>88.59999999999999</v>
+          <t>ТД1--011549/1</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>(16, 6, 8, 630)</t>
+        </is>
       </c>
       <c r="F137" t="n">
-        <v>97.12230518651501</v>
-      </c>
-      <c r="G137" s="2" t="n">
-        <v>45275</v>
+        <v>1.59</v>
+      </c>
+      <c r="G137" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>45393</v>
       </c>
     </row>
     <row r="138">
@@ -3263,81 +4206,119 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C138" t="n">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ТД1--010242/6</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
+          <t>ТД1--013270/1</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>(16, 4, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="G138" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>45401</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C139" t="n">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ТД1--010242/10</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
+          <t>ТД1--010686/1+</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>(16, 3.0, 8.0, 630)</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="G139" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C140" t="n">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ТД1--010242/4</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
+          <t>ТД1--010686/1</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>(16, 7, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="G140" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>45387</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C141" t="n">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ТД1--010248/2</t>
-        </is>
-      </c>
-      <c r="E141" t="n">
-        <v>93.40000000000001</v>
+          <t>ТД1--011067/1+</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>(16, 4.0, 8.0, 630)</t>
+        </is>
       </c>
       <c r="F141" t="n">
-        <v>97.12230518651501</v>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>45275</v>
+        <v>1.4</v>
+      </c>
+      <c r="G141" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>45391</v>
       </c>
     </row>
     <row r="142">
@@ -3345,43 +4326,59 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C142" t="n">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ТД1--012154/2</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
+          <t>ТД1--011067/1</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>(16, 8, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G142" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>45391</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C143" t="n">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ТД1--010634/2</t>
-        </is>
-      </c>
-      <c r="E143" t="n">
-        <v>90.88</v>
+          <t>ТД1--005811/1+</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>(16, 4.0, 8.0, 630)</t>
+        </is>
       </c>
       <c r="F143" t="n">
-        <v>97.12230518651501</v>
-      </c>
-      <c r="G143" s="2" t="n">
-        <v>45275</v>
+        <v>2.38</v>
+      </c>
+      <c r="G143" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>45346</v>
       </c>
     </row>
     <row r="144">
@@ -3389,81 +4386,119 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C144" t="n">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ТД1--010242/5</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
+          <t>ТД1--005811/1</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>(16, 8, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="G144" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>45346</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C145" t="n">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ТД1--010840/4</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
+          <t>ТД1--012317/8</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>(16, 4, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>5</v>
+      </c>
+      <c r="G145" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>45407</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C146" t="n">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ТД1--013217/14</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
+          <t>ТД1--011997/1</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>(16, 3, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>7</v>
+      </c>
+      <c r="G146" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>45394</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C147" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ТД1--010840/2</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
-        <v>55</v>
+          <t>ТД1--012500/1</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>(16, 4, 8, 630)</t>
+        </is>
       </c>
       <c r="F147" t="n">
-        <v>97.12230518651501</v>
-      </c>
-      <c r="G147" s="2" t="n">
-        <v>45275</v>
+        <v>37.62</v>
+      </c>
+      <c r="G147" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>45400</v>
       </c>
     </row>
     <row r="148">
@@ -3471,43 +4506,53 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C148" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ТД1--013217/16</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
+          <t>ТД1--011860/1</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>(16, 4, 8, 630)</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C149" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ТД1--052061/14</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
-        <v>52.6</v>
+          <t>ТД1--010966/2</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>(16, 4, 8, 630)</t>
+        </is>
       </c>
       <c r="F149" t="n">
-        <v>67.80149153191225</v>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>45289</v>
+        <v>38.3904926074233</v>
+      </c>
+      <c r="G149" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>45393</v>
       </c>
     </row>
     <row r="150">
@@ -3515,214 +4560,305 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C150" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ТД1--052061/19</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
+          <t>ТД1--010966/2</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>(16, 4, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>19.53</v>
+      </c>
+      <c r="G150" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>45400</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C151" t="n">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ТД1--052061/23</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
+          <t>ТД1--010410/1</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>(16, 4, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G151" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>45400</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C152" t="n">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ТД1--052061/27</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
+          <t>ТД1--011860/2</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>(16, 8, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G152" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>45397</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C153" t="n">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ТД1--006997/4</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
+          <t>ТД1--009012/2</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>(16, 8, 8, 630)</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C154" t="n">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ТД1--006997/8</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
+          <t>ТД1--013456/1</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>(16, 8, 8, 630)</t>
+        </is>
+      </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
         <v>153</v>
       </c>
       <c r="B155" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C155" t="n">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ТД1--006997/13</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
+          <t>ТД1--013389/1</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>(16, 6, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>10</v>
+      </c>
+      <c r="G155" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>45403</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C156" t="n">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ТД1--006997/14</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr"/>
+          <t>ТД1--010849/1</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>(16, 6, 8, 630)</t>
+        </is>
+      </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C157" t="n">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ТД1--006997/17</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
+          <t>ТД1--010360/1</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>(16, 4, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>37</v>
+      </c>
+      <c r="G157" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>45394</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C158" t="n">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ТД1--006997/18</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr"/>
+          <t>ТД1--009012/4</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>(16, 4, 8, 630)</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
         <v>157</v>
       </c>
       <c r="B159" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C159" t="n">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ТД1--006997/19</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
+          <t>ТД1--012097/1</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>(16, 6, 8, 630)</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="G159" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>45398</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
         <v>158</v>
       </c>
       <c r="B160" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C160" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ТД1--012164/1</t>
-        </is>
-      </c>
-      <c r="E160" t="n">
-        <v>8</v>
+          <t>ТД1--012097/1</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>(16, 6, 8, 630)</t>
+        </is>
       </c>
       <c r="F160" t="n">
-        <v>51.1873234765644</v>
-      </c>
-      <c r="G160" s="2" t="n">
-        <v>45404</v>
+        <v>11.61</v>
+      </c>
+      <c r="G160" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>45398</v>
       </c>
     </row>
     <row r="161">
@@ -3730,87 +4866,113 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C161" t="n">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ТД1--010541/1</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
+          <t>ТД1--056558/27</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>(16, 4, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G161" t="n">
+        <v>43.87484869419806</v>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>45362</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C162" t="n">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ТД1--010242/19</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
+          <t>ТД1--013217/20</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>(16, 6, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G162" t="n">
+        <v>43.87484869419806</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>45429</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C163" t="n">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ТД1--006432/7</t>
-        </is>
-      </c>
-      <c r="E163" t="n">
-        <v>1</v>
-      </c>
-      <c r="F163" t="n">
-        <v>38.3904926074233</v>
-      </c>
-      <c r="G163" s="2" t="n">
-        <v>45388</v>
-      </c>
+          <t>ТД1--013217/19</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>(16, 6, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C164" t="n">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ТД1--009063/4</t>
-        </is>
-      </c>
-      <c r="E164" t="n">
-        <v>36</v>
+          <t>ТД1--012362/1</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>(16, 4, 7, 630)</t>
+        </is>
       </c>
       <c r="F164" t="n">
-        <v>83.46132774006608</v>
-      </c>
-      <c r="G164" s="2" t="n">
-        <v>45396</v>
+        <v>28.34</v>
+      </c>
+      <c r="G164" t="n">
+        <v>43.87484869419806</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>45405</v>
       </c>
     </row>
     <row r="165">
@@ -3818,49 +4980,53 @@
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C165" t="n">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ТД1--009058/5</t>
-        </is>
-      </c>
-      <c r="E165" t="n">
-        <v>35.64</v>
-      </c>
-      <c r="F165" t="n">
-        <v>82.85543988645556</v>
-      </c>
-      <c r="G165" s="2" t="n">
-        <v>45397</v>
-      </c>
+          <t>ТД1--013217/18</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>(16, 4, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
         <v>164</v>
       </c>
       <c r="B166" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C166" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ТД1--009058/3</t>
-        </is>
-      </c>
-      <c r="E166" t="n">
-        <v>10.1</v>
+          <t>ТД1--012164/2</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>(16, 3, 7, 630)</t>
+        </is>
       </c>
       <c r="F166" t="n">
-        <v>68.70249815154163</v>
-      </c>
-      <c r="G166" s="2" t="n">
-        <v>45397</v>
+        <v>14</v>
+      </c>
+      <c r="G166" t="n">
+        <v>38.3904926074233</v>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>45404</v>
       </c>
     </row>
     <row r="167">
@@ -3868,74 +5034,77 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C167" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ТД1--009058/4</t>
-        </is>
-      </c>
-      <c r="E167" t="n">
-        <v>79.05</v>
-      </c>
-      <c r="F167" t="n">
-        <v>82.85543988645556</v>
-      </c>
-      <c r="G167" s="2" t="n">
-        <v>45397</v>
-      </c>
+          <t>ТД1--010242/17</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>(16, 3, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C168" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ТД1--009063/3</t>
-        </is>
-      </c>
-      <c r="E168" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F168" t="n">
-        <v>68.70249815154163</v>
-      </c>
-      <c r="G168" s="2" t="n">
-        <v>45396</v>
-      </c>
+          <t>ТД1--010242/16</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>(16, 3, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C169" t="n">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ТД1--010714/2</t>
-        </is>
-      </c>
-      <c r="E169" t="n">
-        <v>25.12</v>
+          <t>ТД1--012317/3</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>(16, 6, 7, 630)</t>
+        </is>
       </c>
       <c r="F169" t="n">
-        <v>58.5990951137035</v>
-      </c>
-      <c r="G169" s="2" t="n">
-        <v>45396</v>
+        <v>7</v>
+      </c>
+      <c r="G169" t="n">
+        <v>43.87484869419806</v>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>45427</v>
       </c>
     </row>
     <row r="170">
@@ -3943,24 +5112,353 @@
         <v>168</v>
       </c>
       <c r="B170" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C170" t="n">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ТД1--010248/3</t>
-        </is>
-      </c>
-      <c r="E170" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="F170" t="n">
-        <v>68.70249815154163</v>
-      </c>
-      <c r="G170" s="2" t="n">
-        <v>45404</v>
+          <t>ТД1--012317/2</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>(16, 6, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" t="n">
+        <v>11</v>
+      </c>
+      <c r="C171" t="n">
+        <v>101</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>ТД1--012317/1</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>(16, 6, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" t="n">
+        <v>11</v>
+      </c>
+      <c r="C172" t="n">
+        <v>101</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ТД1--010251/3</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>(16, 6, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" t="n">
+        <v>4</v>
+      </c>
+      <c r="C173" t="n">
+        <v>102</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ТД1--012317/4</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>(16, 4, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G173" t="n">
+        <v>43.87484869419806</v>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>45427</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" t="n">
+        <v>4</v>
+      </c>
+      <c r="C174" t="n">
+        <v>102</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ТД1--011882/15</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>(16, 4, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" t="n">
+        <v>11</v>
+      </c>
+      <c r="C175" t="n">
+        <v>103</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ТД1--012317/6</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>(16, 6, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>9</v>
+      </c>
+      <c r="G175" t="n">
+        <v>43.87484869419806</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>45427</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" t="n">
+        <v>11</v>
+      </c>
+      <c r="C176" t="n">
+        <v>103</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>ТД1--010273/1</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>(16, 6, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" t="n">
+        <v>13</v>
+      </c>
+      <c r="C177" t="n">
+        <v>104</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>ТД1--012317/7</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>(16, 3, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>10</v>
+      </c>
+      <c r="G177" t="n">
+        <v>43.87484869419806</v>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>45407</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" t="n">
+        <v>11</v>
+      </c>
+      <c r="C178" t="n">
+        <v>105</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>ТД1--010561/4</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>(16, 6, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>4</v>
+      </c>
+      <c r="G178" t="n">
+        <v>43.87484869419806</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>45416</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" t="n">
+        <v>4</v>
+      </c>
+      <c r="C179" t="n">
+        <v>106</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ТД1--010561/6</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>(16, 4, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>17</v>
+      </c>
+      <c r="G179" t="n">
+        <v>43.87484869419806</v>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>45416</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" t="n">
+        <v>4</v>
+      </c>
+      <c r="C180" t="n">
+        <v>106</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ТД1--010251/1</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>(16, 4, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" t="n">
+        <v>5</v>
+      </c>
+      <c r="C181" t="n">
+        <v>107</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ТД1--010849/2</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>(16, 7, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G181" t="n">
+        <v>43.87484869419806</v>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>45387</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" t="n">
+        <v>4</v>
+      </c>
+      <c r="C182" t="n">
+        <v>108</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ТД1--012763/1</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>(16, 4, 7, 630)</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>2</v>
+      </c>
+      <c r="G182" t="n">
+        <v>43.87484869419806</v>
+      </c>
+      <c r="H182" s="2" t="n">
+        <v>45414</v>
       </c>
     </row>
   </sheetData>
